--- a/fg_test_results.xlsx
+++ b/fg_test_results.xlsx
@@ -1,34 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icortesmarquez\Desktop\Playwright\HO_PW\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FB9035-7DAE-4582-8BB6-FCA65F51D7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="h03" sheetId="2" r:id="rId2"/>
+    <sheet name="h03t" sheetId="3" r:id="rId3"/>
+    <sheet name="wind" sheetId="4" r:id="rId4"/>
+    <sheet name="vh1" sheetId="5" r:id="rId5"/>
+    <sheet name="vh2" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+  <si>
+    <t>User Name</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Product Type</t>
+  </si>
+  <si>
+    <t>Coverage A Limit</t>
+  </si>
+  <si>
+    <t>Quote Number</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>brk99102</t>
+  </si>
+  <si>
+    <t>12274 Accipiter Dr, Orlando, FL 32837</t>
+  </si>
+  <si>
+    <t>HO-3</t>
+  </si>
+  <si>
+    <t>800,000</t>
+  </si>
+  <si>
+    <t>QD20045288</t>
+  </si>
+  <si>
+    <t>$3,751.55</t>
+  </si>
+  <si>
+    <t>15443 Perdido Dr, Orlando, FL 32828</t>
+  </si>
+  <si>
+    <t>Short-Term Vacant or Unoccupied Dwelling - Broad Form</t>
+  </si>
+  <si>
+    <t>600,000</t>
+  </si>
+  <si>
+    <t>QD20045291</t>
+  </si>
+  <si>
+    <t>$3,369.35</t>
+  </si>
+  <si>
+    <t>9426 Meadow Crest Ln, Clermont, FL 34711</t>
+  </si>
+  <si>
+    <t>HO-3 Tenant</t>
+  </si>
+  <si>
+    <t>QD20045292</t>
+  </si>
+  <si>
+    <t>$4,587.35</t>
+  </si>
+  <si>
+    <t>8050 Princeton Dr, Naples, FL 34104</t>
+  </si>
+  <si>
+    <t>QD20045295</t>
+  </si>
+  <si>
+    <t>$6,880.55</t>
+  </si>
+  <si>
+    <t>8329 Lakemont Dr, Jacksonville, FL 32216</t>
+  </si>
+  <si>
+    <t>HO Wind Only</t>
+  </si>
+  <si>
+    <t>QD20045297</t>
+  </si>
+  <si>
+    <t>$4,303.95</t>
+  </si>
+  <si>
+    <t>3618 Elm St, Ellenton, FL 34222</t>
+  </si>
+  <si>
+    <t>Short-Term Vacant or Unoccupied Dwelling - Basic Form</t>
+  </si>
+  <si>
+    <t>QD20045298</t>
+  </si>
+  <si>
+    <t>$2,987.15</t>
+  </si>
+  <si>
+    <t>4111 1111 1111 1111</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,82 +159,299 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>234193</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07D811E9-53F8-54ED-BAC5-5F29032D84B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8158993" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>234193</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42DF3F85-33EB-07E0-5AA5-6C66B55077A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8158993" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>234193</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA619D3-F4DF-537B-2B29-CAAD2AA9D7DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8158993" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>234193</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C442F9F-E568-9D53-A728-EE954F5E77BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8158993" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>234193</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64FC488B-8ECE-E5C9-3D54-2562CC47A3D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8158993" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,207 +738,209 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>User Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Product Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Coverage A Limit</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Quote Number</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>brk99102</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>12274 Accipiter Dr, Orlando, FL 32837</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HO-3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>800,000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>QD20045288</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>$3,751.55</t>
-        </is>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>brk99102</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>15443 Perdido Dr, Orlando, FL 32828</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Short-Term Vacant or Unoccupied Dwelling - Broad Form</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>600,000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>QD20045291</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>$3,369.35</t>
-        </is>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>brk99102</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>9426 Meadow Crest Ln, Clermont, FL 34711</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HO-3 Tenant</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>800,000</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>QD20045292</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>$4,587.35</t>
-        </is>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>brk99102</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>8050 Princeton Dr, Naples, FL 34104</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HO-3 Tenant</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>800,000</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>QD20045295</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>$6,880.55</t>
-        </is>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>brk99102</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>8329 Lakemont Dr, Jacksonville, FL 32216</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HO Wind Only</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>800,000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>QD20045297</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>$4,303.95</t>
-        </is>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97FFDC8-5325-4CA9-B0DB-85CDE0229545}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1BD1FF-7A41-42AD-BC64-086EE509B685}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5E4832-3443-4CA1-8890-251B28AAEDCE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC93AC30-EB05-472F-90D6-E9070F96B762}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D694F74-D45B-4ED4-84B8-ABE90EB88794}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/fg_test_results.xlsx
+++ b/fg_test_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9607 Bahia Rd, Ocala, FL 34472</t>
+          <t>15110 Shearcrest Dr, Lithia, FL 33547</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HO-3</t>
+          <t>HO Wind Only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -471,12 +471,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>QD20045309</t>
+          <t>QD20045356</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$7,904.30</t>
+          <t>$3,175.20</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7733 Belvoir Dr, Orlando, FL 32835</t>
+          <t>612 Citrus Wood Ln, Valrico, FL 33594</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HO-3 Tenant</t>
+          <t>HO Wind Only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>QD20045310</t>
+          <t>QD20045358</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$5,708.75</t>
+          <t>$3,597.30</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8734 Crestgate Cir, Orlando, FL 32819</t>
+          <t>12274 Accipiter Dr, Orlando, FL 32837</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -535,76 +535,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>QD20045311</t>
+          <t>QD20045359</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$8,447.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tsicortesmarquez@geovera</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3319 Clubview Dr, North Fort Myers, FL 33917</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Short-Term Vacant or Unoccupied Dwelling - Basic Form</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>600,000</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>QD20045312</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>$9,146.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tsicortesmarquez@geovera</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3408 69th St W, Lehigh Acres, FL 33971</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Short-Term Vacant or Unoccupied Dwelling - Broad Form</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>600,000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>QD20045313</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>$3,179.30</t>
+          <t>$3,824.10</t>
         </is>
       </c>
     </row>

--- a/fg_test_results.xlsx
+++ b/fg_test_results.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="36" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="51.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="16" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -541,6 +547,198 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>$3,824.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8832 Savona Ct, Naples, FL 34119</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HO-3 Tenant</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>QD20045360</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>$4,493.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8832 Savona Ct, Naples, FL 34119</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HO Wind Only</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>QD20045361</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>$3,920.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3419 26th St SW, Lehigh Acres, FL 33976</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Short-Term Vacant or Unoccupied Dwelling - Basic Form</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>600,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>QD20045362</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>$2,527.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>612 Citrus Wood Ln, Valrico, FL 33594</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HO Wind Only</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>QD20045364</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>$3,597.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9426 Meadow Crest Ln, Clermont, FL 34711</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HO-3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>QD20045365</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>$4,675.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3618 Elm St, Ellenton, FL 34222</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Short-Term Vacant or Unoccupied Dwelling - Broad Form</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>600,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>QD20045366</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>$3,365.15</t>
         </is>
       </c>
     </row>

--- a/fg_test_results.xlsx
+++ b/fg_test_results.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -742,6 +742,38 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tsicortesmarquez@geovera</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12274 Accipiter Dr, Orlando, FL 32837</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HO Wind Only</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>QD20045367</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>$3,824.10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
